--- a/dist/entrée.xlsx
+++ b/dist/entrée.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25601"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7843221B-88DF-4A56-B250-D821BC82531E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BEA4B38-9AC1-4E16-973E-B30E1F560D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2625" yWindow="60" windowWidth="17340" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14895" yWindow="2955" windowWidth="17340" windowHeight="15435" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="menu_1" sheetId="7" r:id="rId1"/>
@@ -1059,7 +1059,7 @@
     <t>9/5/2022</t>
   </si>
   <si>
-    <t>09/05/2022</t>
+    <t>10/31/2022</t>
   </si>
 </sst>
 </file>
@@ -1725,7 +1725,7 @@
     </row>
     <row r="2" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" s="32" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B2" s="17">
         <v>22</v>
@@ -2517,7 +2517,7 @@
     </row>
     <row r="2" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" s="32" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B2" s="17">
         <v>22</v>

--- a/dist/entrée.xlsx
+++ b/dist/entrée.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25601"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BEA4B38-9AC1-4E16-973E-B30E1F560D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28C165D2-4950-4649-B00F-A8639148546D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14895" yWindow="2955" windowWidth="17340" windowHeight="15435" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="menu_1" sheetId="7" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="342">
   <si>
     <t>semaine</t>
   </si>
@@ -1057,9 +1057,6 @@
   </si>
   <si>
     <t>9/5/2022</t>
-  </si>
-  <si>
-    <t>10/31/2022</t>
   </si>
 </sst>
 </file>
@@ -2517,7 +2514,7 @@
     </row>
     <row r="2" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" s="32" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B2" s="17">
         <v>22</v>

--- a/dist/entrée.xlsx
+++ b/dist/entrée.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25601"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28C165D2-4950-4649-B00F-A8639148546D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1975913F-AF0E-4CE1-9642-F12A541AA286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14895" yWindow="2955" windowWidth="17340" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="menu_1" sheetId="7" r:id="rId1"/>
